--- a/manuscript_material/on_demand/Source_Data_OD_Fig4.xlsx
+++ b/manuscript_material/on_demand/Source_Data_OD_Fig4.xlsx
@@ -507,22 +507,22 @@
         <v>150</v>
       </c>
       <c r="D3" t="n">
-        <v>87.56</v>
+        <v>86.89</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>87.33</v>
       </c>
       <c r="F3" t="n">
         <v>0.44</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.29</v>
+        <v>-4.08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.29</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="4">
@@ -567,22 +567,22 @@
         <v>150</v>
       </c>
       <c r="D5" t="n">
-        <v>90.89</v>
+        <v>91.11</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>92.67</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="G5" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.72</v>
+        <v>-1.96</v>
       </c>
       <c r="I5" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="6">
@@ -627,22 +627,22 @@
         <v>150</v>
       </c>
       <c r="D7" t="n">
+        <v>85.56</v>
+      </c>
+      <c r="E7" t="n">
         <v>85.33</v>
       </c>
-      <c r="E7" t="n">
-        <v>84.67</v>
-      </c>
       <c r="F7" t="n">
-        <v>-0.67</v>
+        <v>-0.22</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.33</v>
+        <v>-2.67</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.44</v>
+        <v>-7.53</v>
       </c>
       <c r="I7" t="n">
-        <v>1.39</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -1287,28 +1287,28 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>86.67</v>
+        <v>85.67</v>
       </c>
       <c r="F13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G13" t="n">
         <v>0.33</v>
       </c>
       <c r="H13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L13" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
@@ -1375,28 +1375,28 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>92.33</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="H15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n">
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="M15" t="n">
         <v>4</v>
@@ -1463,31 +1463,31 @@
         <v>100</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>85.33</v>
       </c>
       <c r="F17" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G17" t="n">
-        <v>-2</v>
+        <v>-1.33</v>
       </c>
       <c r="H17" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" t="n">
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L17" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="M17" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -22519,11 +22519,11 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>1; 1; 1</t>
+          <t>1; 1; 0</t>
         </is>
       </c>
       <c r="F543" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G543" t="n">
         <v>1</v>
@@ -22709,11 +22709,11 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>0; 0; 0</t>
+          <t>1; 0; 0</t>
         </is>
       </c>
       <c r="F548" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="G548" t="n">
         <v>0</v>
@@ -23773,11 +23773,11 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>1; 1; 1</t>
+          <t>1; 0; 1</t>
         </is>
       </c>
       <c r="F576" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G576" t="n">
         <v>1</v>
@@ -24571,11 +24571,11 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>0; 0; 0</t>
+          <t>0; 0; 1</t>
         </is>
       </c>
       <c r="F597" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="G597" t="n">
         <v>0</v>
@@ -28865,18 +28865,18 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>0; 1; 1</t>
+          <t>0; 1; 0</t>
         </is>
       </c>
       <c r="F710" t="n">
-        <v>0.6667</v>
+        <v>0.3333</v>
       </c>
       <c r="G710" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Majority answer correct</t>
+          <t>No majority (three different answers)</t>
         </is>
       </c>
     </row>
@@ -29511,11 +29511,11 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>1; 1; 0</t>
+          <t>1; 1; 1</t>
         </is>
       </c>
       <c r="F727" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="G727" t="n">
         <v>1</v>
@@ -29549,18 +29549,18 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>1; 0; 0</t>
+          <t>1; 0; 1</t>
         </is>
       </c>
       <c r="F728" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="G728" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Majority answer incorrect</t>
+          <t>Majority answer correct</t>
         </is>
       </c>
     </row>
@@ -29587,11 +29587,11 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>1; 1; 0</t>
+          <t>1; 1; 1</t>
         </is>
       </c>
       <c r="F729" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="G729" t="n">
         <v>1</v>
@@ -29929,18 +29929,18 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>0; 0; 0</t>
+          <t>0; 0; 1</t>
         </is>
       </c>
       <c r="F738" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="G738" t="n">
         <v>0</v>
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>No majority (three different answers)</t>
+          <t>Majority answer incorrect</t>
         </is>
       </c>
     </row>
@@ -30309,18 +30309,18 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>0; 1; 1</t>
+          <t>0; 0; 0</t>
         </is>
       </c>
       <c r="F748" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="G748" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Majority answer correct</t>
+          <t>No majority (three different answers)</t>
         </is>
       </c>
     </row>
@@ -31042,7 +31042,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>No majority (three different answers)</t>
+          <t>Majority answer incorrect</t>
         </is>
       </c>
     </row>
@@ -31297,11 +31297,11 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>1; 1; 1</t>
+          <t>1; 1; 0</t>
         </is>
       </c>
       <c r="F774" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G774" t="n">
         <v>1</v>
@@ -31639,11 +31639,11 @@
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>1; 1; 1</t>
+          <t>1; 0; 1</t>
         </is>
       </c>
       <c r="F783" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G783" t="n">
         <v>1</v>
@@ -31867,11 +31867,11 @@
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>1; 1; 1</t>
+          <t>1; 1; 0</t>
         </is>
       </c>
       <c r="F789" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G789" t="n">
         <v>1</v>
@@ -32133,11 +32133,11 @@
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>1; 1; 1</t>
+          <t>1; 1; 0</t>
         </is>
       </c>
       <c r="F796" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="G796" t="n">
         <v>1</v>
@@ -37111,18 +37111,18 @@
       </c>
       <c r="E927" t="inlineStr">
         <is>
-          <t>0; 0; 1</t>
+          <t>1; 0; 1</t>
         </is>
       </c>
       <c r="F927" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="G927" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H927" t="inlineStr">
         <is>
-          <t>No majority (three different answers)</t>
+          <t>Majority answer correct</t>
         </is>
       </c>
     </row>
@@ -44787,18 +44787,18 @@
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>1; 0; 0</t>
+          <t>1; 0; 1</t>
         </is>
       </c>
       <c r="F1129" t="n">
-        <v>0.3333</v>
+        <v>0.6667</v>
       </c>
       <c r="G1129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1129" t="inlineStr">
         <is>
-          <t>No majority (three different answers)</t>
+          <t>Majority answer correct</t>
         </is>
       </c>
     </row>
